--- a/data/TBI_Clinical_Rules.xlsx
+++ b/data/TBI_Clinical_Rules.xlsx
@@ -4,19 +4,19 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Item Trigger Rules"/>
     <sheet r:id="rId2" sheetId="2" name="Shootdown Redundancy Logic"/>
-    <sheet r:id="rId3" sheetId="3" name="Priority Ranking &amp;amp; Weight"/>
+    <sheet r:id="rId3" sheetId="3" name="Priority Ranking &amp;amp;amp; Weight"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>Item Priority Ranking — Knapsack Packing Order (10 lb drone limit)</t>
   </si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>Clinical Rationale</t>
-  </si>
-  <si>
-    <t>TBI Monitoring Kit</t>
   </si>
   <si>
     <t>4.0</t>
@@ -375,7 +372,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,6 +384,12 @@
       <sz val="14"/>
       <color rgb="FFffffff"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -461,7 +464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -482,6 +485,13 @@
       <bottom style="thin">
         <color rgb="FFc6c6c6"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -508,6 +518,93 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -517,100 +614,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -978,27 +988,27 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="29.25" customFormat="1" s="6">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="75.75" customFormat="1" s="6">
       <c r="A4" s="19">
         <v>1</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>81</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>82</v>
       </c>
       <c r="H4" s="19">
         <v>1</v>
@@ -1015,16 +1025,16 @@
         <v>14</v>
       </c>
       <c r="D5" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="F5" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="H5" s="22">
         <v>2</v>
@@ -1041,16 +1051,16 @@
         <v>8</v>
       </c>
       <c r="D6" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="F6" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="20" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>89</v>
       </c>
       <c r="H6" s="19">
         <v>1</v>
@@ -1067,16 +1077,16 @@
         <v>17</v>
       </c>
       <c r="D7" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>91</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>92</v>
       </c>
       <c r="H7" s="22">
         <v>3</v>
@@ -1093,16 +1103,16 @@
         <v>26</v>
       </c>
       <c r="D8" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="H8" s="19">
         <v>5</v>
@@ -1119,16 +1129,16 @@
         <v>38</v>
       </c>
       <c r="D9" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="F9" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="G9" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>98</v>
       </c>
       <c r="H9" s="22">
         <v>9</v>
@@ -1145,16 +1155,16 @@
         <v>20</v>
       </c>
       <c r="D10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="F10" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="20" t="s">
         <v>100</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>101</v>
       </c>
       <c r="H10" s="19">
         <v>4</v>
@@ -1171,22 +1181,22 @@
         <v>11</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="G11" s="23" t="s">
         <v>103</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>104</v>
       </c>
       <c r="H11" s="22">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="70" customFormat="1" s="6">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="41.25" customFormat="1" s="6">
       <c r="A12" s="19">
         <v>9</v>
       </c>
@@ -1197,16 +1207,16 @@
         <v>23</v>
       </c>
       <c r="D12" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="F12" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="H12" s="19">
         <v>4</v>
@@ -1223,16 +1233,16 @@
         <v>32</v>
       </c>
       <c r="D13" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="F13" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="23" t="s">
         <v>109</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>110</v>
       </c>
       <c r="H13" s="22">
         <v>7</v>
@@ -1249,16 +1259,16 @@
         <v>35</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>111</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>112</v>
       </c>
       <c r="H14" s="19">
         <v>8</v>
